--- a/Dynamic2.xlsx
+++ b/Dynamic2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://enctc-my.sharepoint.com/personal/pao0918_ntpc_edu_tw/Documents/Analysis/DASHBOARD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="8_{7176EC51-8657-4EB6-9FF7-077E03CB3441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46142DB9-F257-4D9E-938C-1FB0A3A4C79A}"/>
+  <xr:revisionPtr revIDLastSave="201" documentId="8_{7176EC51-8657-4EB6-9FF7-077E03CB3441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2FE82F7-0D54-4FAF-8189-FDDEB176DDA3}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="890" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="金控_ROE" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="58">
   <si>
     <t>名稱</t>
   </si>
@@ -272,328 +272,6 @@
         <charset val="136"/>
       </rPr>
       <t>市占率</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>202</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>0全年成交金額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>億)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>202</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>市占率</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2021</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>全年成交金額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>億)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2021</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>市占率</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2022</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>全年成交金額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>億)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2022</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>市占率</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2023</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>全年成交金額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>億)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2023</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>市占率</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>全年成交金額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>億)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2024</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>市占率</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>/1-6月成交金額</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="MS Gothic"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>億)</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2025</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="細明體"/>
-        <family val="3"/>
-        <charset val="136"/>
-      </rPr>
-      <t>/1-6月市占率</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -978,8 +656,8 @@
     <numFmt numFmtId="180" formatCode="###,###,###,##0.00"/>
     <numFmt numFmtId="181" formatCode="0.00_)"/>
     <numFmt numFmtId="182" formatCode="##0.00"/>
-    <numFmt numFmtId="187" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="188" formatCode="[$-409]d\-mmm;@"/>
+    <numFmt numFmtId="183" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="184" formatCode="[$-409]d\-mmm;@"/>
   </numFmts>
   <fonts count="44">
     <font>
@@ -2227,8 +1905,8 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="183" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="184" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="186">
     <cellStyle name="20% - 輔色1 2" xfId="5" xr:uid="{7A86E234-8DA3-4A16-8047-6F87340A4069}"/>
@@ -2730,7 +2408,7 @@
         <v>2024</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H1" s="31">
         <v>45838.5</v>
@@ -2927,7 +2605,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2">
         <v>7.94</v>
@@ -2954,7 +2632,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2">
         <v>9.0500000000000007</v>
@@ -3062,7 +2740,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2">
         <v>2.39</v>
@@ -3289,17 +2967,17 @@
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="26.42578125" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="26.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="26.42578125" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="29" customWidth="1"/>
     <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3308,40 +2986,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="M1" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -3633,7 +3311,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B9" s="25">
         <v>45385.551299999999</v>
@@ -3920,7 +3598,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B16" s="23">
         <v>26063.710800000001</v>
@@ -3961,7 +3639,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B17" s="23">
         <f t="shared" ref="B17:L17" si="0">B5+B9</f>
@@ -4014,7 +3692,7 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B18" s="23">
         <v>44295.381699999998</v>
@@ -4065,21 +3743,21 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
-    <col min="2" max="2" width="50.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="50.7109375" customWidth="1"/>
     <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="26.42578125" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="26.42578125" customWidth="1"/>
     <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="26.42578125" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="26.42578125" customWidth="1"/>
     <col min="7" max="7" width="17.42578125" customWidth="1"/>
-    <col min="8" max="8" width="26.42578125" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="26.42578125" customWidth="1"/>
     <col min="9" max="9" width="17.42578125" customWidth="1"/>
-    <col min="10" max="10" width="27.7109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="27.7109375" customWidth="1"/>
     <col min="11" max="11" width="17.42578125" customWidth="1"/>
-    <col min="12" max="12" width="26.7109375" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="26.7109375" customWidth="1"/>
     <col min="13" max="13" width="21.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4088,40 +3766,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -4413,7 +4091,7 @@
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B9" s="25">
         <v>157725595072</v>
@@ -4632,7 +4310,7 @@
       <c r="K14" s="26"/>
       <c r="L14" s="25"/>
       <c r="M14" s="27" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -4678,7 +4356,7 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B16" s="25">
         <f t="shared" ref="B16:L16" si="0">B5+B9</f>
@@ -4728,6 +4406,9 @@
         <f>M5+M9</f>
         <v>4.4299999999999999E-2</v>
       </c>
+    </row>
+    <row r="27" spans="7:7">
+      <c r="G27" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4769,7 +4450,7 @@
         <v>2024</v>
       </c>
       <c r="G1" s="30" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H1" s="31">
         <v>45838.5</v>
@@ -4777,7 +4458,7 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B2" s="2">
         <v>4.22</v>
@@ -4804,7 +4485,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="B3" s="2">
         <v>3.02</v>
@@ -4831,7 +4512,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2">
         <v>6.35</v>
@@ -4858,7 +4539,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2">
         <v>5.61</v>
@@ -4885,7 +4566,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B6" s="2">
         <v>4.3</v>
@@ -4912,7 +4593,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="B7" s="2">
         <v>6.44</v>
@@ -4939,7 +4620,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2">
         <v>6.93</v>
@@ -4966,7 +4647,7 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2">
         <v>7.16</v>
@@ -4993,7 +4674,7 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2">
         <v>6.24</v>
@@ -5020,7 +4701,7 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2">
         <v>7.72</v>
@@ -5047,7 +4728,7 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2">
         <v>8.8000000000000007</v>
@@ -5074,7 +4755,7 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B13" s="2">
         <v>7.14</v>
@@ -5101,7 +4782,7 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B14" s="2">
         <v>8.57</v>
@@ -5128,7 +4809,7 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="B15" s="2">
         <v>9.4499999999999993</v>
@@ -5155,7 +4836,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="B16" s="2">
         <v>8.77</v>
@@ -5182,7 +4863,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="B17" s="2">
         <v>9.32</v>
@@ -5249,7 +4930,7 @@
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
     <col min="2" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5645,7 +5326,7 @@
     </row>
     <row r="16" spans="1:8" ht="27">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G16" s="11">
         <f>G9+G5</f>
@@ -6069,7 +5750,7 @@
     </row>
     <row r="16" spans="1:8" ht="27">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G16" s="11">
         <f>G9+G5</f>
@@ -6493,7 +6174,7 @@
     </row>
     <row r="16" spans="1:8" ht="27">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B16" s="29">
         <v>0</v>
@@ -6932,7 +6613,7 @@
     </row>
     <row r="16" spans="1:8" ht="27">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="G16" s="11">
         <f>G9+G5</f>
@@ -7356,7 +7037,7 @@
     </row>
     <row r="16" spans="1:8" ht="27">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B16" s="29">
         <v>7.4035558021400156</v>
@@ -7398,15 +7079,12 @@
   <sheetFormatPr defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.28515625" hidden="1" customWidth="1"/>
-    <col min="3" max="4" width="19.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19.28515625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="19.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.28515625" customWidth="1"/>
     <col min="9" max="9" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="16.140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="15.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7952,7 +7630,7 @@
     </row>
     <row r="16" spans="1:12" ht="27">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D16" s="29">
         <v>0</v>
@@ -7995,7 +7673,7 @@
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="5" width="19.28515625" customWidth="1"/>
     <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="15.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8391,7 +8069,7 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B16" s="29">
         <v>7.5053786393587201</v>
